--- a/public/doc/智慧党建.xlsx
+++ b/public/doc/智慧党建.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12680"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="创岗建区评定结果" sheetId="2" r:id="rId1"/>
+    <sheet name="党小组考核结果" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="22">
   <si>
     <t>“创岗建区”季度评定结果</t>
   </si>
@@ -171,18 +172,47 @@
     <t>区</t>
   </si>
   <si>
-    <t>四优</t>
+    <t>党员安全之星</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
+    <t>四优党员</t>
+  </si>
+  <si>
+    <t>张三</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>李四</t>
+  </si>
+  <si>
+    <t>王五</t>
+  </si>
+  <si>
+    <t>……</t>
+  </si>
+  <si>
+    <r>
+      <t>注：</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>注：</t>
+      <t>先锋岗用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
     </r>
     <r>
       <rPr>
@@ -191,7 +221,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>先锋岗用</t>
+      <t>表示、 达标岗用</t>
     </r>
     <r>
       <rPr>
@@ -200,7 +230,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>1</t>
+      <t>2</t>
     </r>
     <r>
       <rPr>
@@ -209,7 +239,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>表示、 达标岗用</t>
+      <t>表示、警示岗用</t>
     </r>
     <r>
       <rPr>
@@ -218,7 +248,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
+      <t>3</t>
     </r>
     <r>
       <rPr>
@@ -227,7 +257,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>表示、警示岗用</t>
+      <t>表示；红旗区用</t>
     </r>
     <r>
       <rPr>
@@ -236,7 +266,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>3</t>
+      <t>4</t>
     </r>
     <r>
       <rPr>
@@ -245,7 +275,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>表示；红旗区用</t>
+      <t>表示、达标区用</t>
     </r>
     <r>
       <rPr>
@@ -254,7 +284,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>4</t>
+      <t>5</t>
     </r>
     <r>
       <rPr>
@@ -263,7 +293,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>表示、达标区用</t>
+      <t>表示、警示区用</t>
     </r>
     <r>
       <rPr>
@@ -272,7 +302,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>5</t>
+      <t>6</t>
     </r>
     <r>
       <rPr>
@@ -281,7 +311,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>表示、警示区用</t>
+      <t>表示；党员安全之星、四优党员用</t>
     </r>
     <r>
       <rPr>
@@ -290,7 +320,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>6</t>
+      <t>√</t>
     </r>
     <r>
       <rPr>
@@ -299,26 +329,23 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>表示；四优用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>√</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>表示。</t>
     </r>
+  </si>
+  <si>
+    <t>党小组考核结果</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>党小组名称</t>
+  </si>
+  <si>
+    <t>XX线路工区党小组</t>
+  </si>
+  <si>
+    <t>优秀</t>
   </si>
 </sst>
 </file>
@@ -331,9 +358,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -908,137 +943,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1048,11 +1083,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1060,16 +1101,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1383,335 +1427,706 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="3" width="10.0673076923077" customWidth="1"/>
+    <col min="2" max="4" width="10.0636363636364" customWidth="1"/>
+    <col min="8" max="8" width="10.0636363636364" customWidth="1"/>
+    <col min="12" max="12" width="10.0636363636364" customWidth="1"/>
+    <col min="16" max="16" width="10.0636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" customHeight="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="51" customHeight="1" spans="1:17">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="39" customHeight="1" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="39" customHeight="1" spans="1:17">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" ht="15.5" customHeight="1" spans="1:13">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" ht="15.5" customHeight="1" spans="1:17">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5" t="s">
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+    </row>
+    <row r="4" ht="27" spans="1:17">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="K4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="L4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="M4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="O4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="P4" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="6"/>
+      <c r="Q4" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9">
+        <v>4</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="9">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q6" s="9"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="9">
+        <v>3</v>
+      </c>
+      <c r="C7" s="9">
+        <v>6</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="6"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="6"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="6"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="6"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="6"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="6"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="6"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="6"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="6"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:13">
-      <c r="A18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" ht="36" customHeight="1"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:17">
+      <c r="A18" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="13"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="A18:Q18"/>
     <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="8.72727272727273" style="1"/>
+    <col min="2" max="2" width="23.8181818181818" style="1" customWidth="1"/>
+    <col min="3" max="6" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="29" customHeight="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:6">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:6">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:6">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:6">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:6">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:6">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:6">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:6">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:6">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:6">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>